--- a/ReciPro/traffic.xlsx
+++ b/ReciPro/traffic.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Views" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Clones" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Referrers" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Popular Paths" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Downloads" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stats" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Views" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Clones" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Referrers" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Popular Paths" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Downloads" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Stats" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -461,7 +461,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O19"/>
+  <dimension ref="A1:O22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -479,62 +479,62 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="8" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B1" s="8" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Total Views</t>
         </is>
       </c>
-      <c r="C1" s="8" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Unique Visitors</t>
         </is>
       </c>
-      <c r="E1" s="8" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Period</t>
         </is>
       </c>
-      <c r="F1" s="8" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Total Views</t>
         </is>
       </c>
-      <c r="G1" s="8" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Unique Visitors</t>
         </is>
       </c>
-      <c r="I1" s="8" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Period</t>
         </is>
       </c>
-      <c r="J1" s="8" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Total Views</t>
         </is>
       </c>
-      <c r="K1" s="8" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Unique Visitors</t>
         </is>
       </c>
-      <c r="M1" s="8" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Period</t>
         </is>
       </c>
-      <c r="N1" s="8" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Total Views</t>
         </is>
       </c>
-      <c r="O1" s="8" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Unique Visitors</t>
         </is>
@@ -543,14 +543,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>78</v>
+        <v>93</v>
       </c>
       <c r="C2" t="n">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -558,10 +558,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>78</v>
+        <v>329</v>
       </c>
       <c r="G2" t="n">
-        <v>39</v>
+        <v>147</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -569,10 +569,10 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>838</v>
+        <v>1089</v>
       </c>
       <c r="K2" t="n">
-        <v>369</v>
+        <v>477</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -580,23 +580,23 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>1078</v>
+        <v>1329</v>
       </c>
       <c r="O2" t="n">
-        <v>480</v>
+        <v>588</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>11</v>
+        <v>86</v>
       </c>
       <c r="C3" t="n">
-        <v>8</v>
+        <v>39</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -624,14 +624,14 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>31</v>
+        <v>72</v>
       </c>
       <c r="C4" t="n">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -648,14 +648,14 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>110</v>
+        <v>78</v>
       </c>
       <c r="C5" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -672,141 +672,141 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>84</v>
+        <v>11</v>
       </c>
       <c r="C6" t="n">
-        <v>42</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>57</v>
+        <v>31</v>
       </c>
       <c r="C7" t="n">
-        <v>31</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>77</v>
+        <v>110</v>
       </c>
       <c r="C8" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="C9" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="C10" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>22</v>
+        <v>77</v>
       </c>
       <c r="C11" t="n">
-        <v>12</v>
+        <v>38</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>82</v>
+        <v>106</v>
       </c>
       <c r="C12" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C13" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="C14" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>62</v>
+        <v>82</v>
       </c>
       <c r="C15" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="C16" t="n">
         <v>32</v>
@@ -815,39 +815,78 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="C17" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>33</v>
+        <v>62</v>
       </c>
       <c r="C18" t="n">
-        <v>10</v>
+        <v>27</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>57</v>
+      </c>
+      <c r="C19" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>28</v>
+      </c>
+      <c r="C20" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>33</v>
+      </c>
+      <c r="C21" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>2026-03-27</t>
         </is>
       </c>
-      <c r="B19" t="n">
+      <c r="B22" t="n">
         <v>60</v>
       </c>
-      <c r="C19" t="n">
+      <c r="C22" t="n">
         <v>26</v>
       </c>
     </row>
@@ -862,7 +901,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O19"/>
+  <dimension ref="A1:O22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -880,62 +919,62 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="8" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B1" s="8" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Total Clones</t>
         </is>
       </c>
-      <c r="C1" s="8" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Unique Cloners</t>
         </is>
       </c>
-      <c r="E1" s="8" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Period</t>
         </is>
       </c>
-      <c r="F1" s="8" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Total Clones</t>
         </is>
       </c>
-      <c r="G1" s="8" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Unique Cloners</t>
         </is>
       </c>
-      <c r="I1" s="8" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Period</t>
         </is>
       </c>
-      <c r="J1" s="8" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Total Clones</t>
         </is>
       </c>
-      <c r="K1" s="8" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Unique Cloners</t>
         </is>
       </c>
-      <c r="M1" s="8" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Period</t>
         </is>
       </c>
-      <c r="N1" s="8" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Total Clones</t>
         </is>
       </c>
-      <c r="O1" s="8" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Unique Cloners</t>
         </is>
@@ -944,14 +983,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>45</v>
+        <v>7</v>
       </c>
       <c r="C2" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -959,10 +998,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>45</v>
+        <v>122</v>
       </c>
       <c r="G2" t="n">
-        <v>30</v>
+        <v>68</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -970,10 +1009,10 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>421</v>
+        <v>498</v>
       </c>
       <c r="K2" t="n">
-        <v>237</v>
+        <v>275</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -981,23 +1020,23 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>494</v>
+        <v>571</v>
       </c>
       <c r="O2" t="n">
-        <v>291</v>
+        <v>329</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3</v>
+        <v>39</v>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -1025,14 +1064,14 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -1049,14 +1088,14 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="C5" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -1073,11 +1112,11 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C6" t="n">
         <v>2</v>
@@ -1086,128 +1125,128 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="C8" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="C9" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>212</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>99</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="C11" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="C12" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>6</v>
+        <v>212</v>
       </c>
       <c r="C13" t="n">
-        <v>5</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="C14" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C16" t="n">
         <v>5</v>
@@ -1216,39 +1255,78 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>18</v>
+        <v>47</v>
       </c>
       <c r="C17" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="C18" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>5</v>
+      </c>
+      <c r="C19" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>18</v>
+      </c>
+      <c r="C20" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>9</v>
+      </c>
+      <c r="C21" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>2026-03-27</t>
         </is>
       </c>
-      <c r="B19" t="n">
+      <c r="B22" t="n">
         <v>14</v>
       </c>
-      <c r="C19" t="n">
+      <c r="C22" t="n">
         <v>9</v>
       </c>
     </row>
@@ -1263,7 +1341,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S61"/>
+  <dimension ref="A1:S71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1285,82 +1363,82 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="8" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Date Collected</t>
         </is>
       </c>
-      <c r="B1" s="8" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Referrer</t>
         </is>
       </c>
-      <c r="C1" s="8" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Total Count</t>
         </is>
       </c>
-      <c r="D1" s="8" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Unique</t>
         </is>
       </c>
-      <c r="F1" s="8" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Period</t>
         </is>
       </c>
-      <c r="G1" s="8" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Referrer</t>
         </is>
       </c>
-      <c r="H1" s="8" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Total Count</t>
         </is>
       </c>
-      <c r="I1" s="8" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Unique</t>
         </is>
       </c>
-      <c r="K1" s="8" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Period</t>
         </is>
       </c>
-      <c r="L1" s="8" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Referrer</t>
         </is>
       </c>
-      <c r="M1" s="8" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Total Count</t>
         </is>
       </c>
-      <c r="N1" s="8" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Unique</t>
         </is>
       </c>
-      <c r="P1" s="8" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Period</t>
         </is>
       </c>
-      <c r="Q1" s="8" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Referrer</t>
         </is>
       </c>
-      <c r="R1" s="8" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Total Count</t>
         </is>
       </c>
-      <c r="S1" s="8" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Unique</t>
         </is>
@@ -1369,7 +1447,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1378,10 +1456,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="D2" t="n">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -1394,10 +1472,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>146</v>
+        <v>296</v>
       </c>
       <c r="I2" t="n">
-        <v>76</v>
+        <v>147</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -1410,10 +1488,10 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>884</v>
+        <v>1034</v>
       </c>
       <c r="N2" t="n">
-        <v>438</v>
+        <v>509</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
@@ -1426,160 +1504,160 @@
         </is>
       </c>
       <c r="R2" t="n">
-        <v>884</v>
+        <v>1034</v>
       </c>
       <c r="S2" t="n">
-        <v>438</v>
+        <v>509</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>Bing</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>49</v>
+      </c>
+      <c r="D3" t="n">
+        <v>27</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2026-W16</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Bing</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>75</v>
+      </c>
+      <c r="I3" t="n">
+        <v>42</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
           <t>github.com</t>
         </is>
       </c>
-      <c r="C3" t="n">
-        <v>34</v>
-      </c>
-      <c r="D3" t="n">
-        <v>17</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>2026-W16</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="M3" t="n">
+        <v>275</v>
+      </c>
+      <c r="N3" t="n">
+        <v>129</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
         <is>
           <t>github.com</t>
         </is>
       </c>
-      <c r="H3" t="n">
-        <v>34</v>
-      </c>
-      <c r="I3" t="n">
-        <v>17</v>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>2026-04</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>github.com</t>
-        </is>
-      </c>
-      <c r="M3" t="n">
-        <v>236</v>
-      </c>
-      <c r="N3" t="n">
-        <v>107</v>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>github.com</t>
-        </is>
-      </c>
       <c r="R3" t="n">
-        <v>236</v>
+        <v>275</v>
       </c>
       <c r="S3" t="n">
-        <v>107</v>
+        <v>129</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>github.com</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>39</v>
+      </c>
+      <c r="D4" t="n">
+        <v>22</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-W16</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>github.com</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>73</v>
+      </c>
+      <c r="I4" t="n">
+        <v>39</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
           <t>Bing</t>
         </is>
       </c>
-      <c r="C4" t="n">
-        <v>26</v>
-      </c>
-      <c r="D4" t="n">
-        <v>15</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>2026-W16</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
+      <c r="M4" t="n">
+        <v>180</v>
+      </c>
+      <c r="N4" t="n">
+        <v>102</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
         <is>
           <t>Bing</t>
         </is>
       </c>
-      <c r="H4" t="n">
-        <v>26</v>
-      </c>
-      <c r="I4" t="n">
-        <v>15</v>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>2026-04</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>Bing</t>
-        </is>
-      </c>
-      <c r="M4" t="n">
-        <v>131</v>
-      </c>
-      <c r="N4" t="n">
-        <v>75</v>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>Bing</t>
-        </is>
-      </c>
       <c r="R4" t="n">
-        <v>131</v>
+        <v>180</v>
       </c>
       <c r="S4" t="n">
-        <v>75</v>
+        <v>102</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>seto77.github.io</t>
+          <t>link.zhihu.com</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>15</v>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1588,64 +1666,64 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
+          <t>link.zhihu.com</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>28</v>
+      </c>
+      <c r="I5" t="n">
+        <v>23</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
           <t>seto77.github.io</t>
         </is>
       </c>
-      <c r="H5" t="n">
-        <v>15</v>
-      </c>
-      <c r="I5" t="n">
-        <v>3</v>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>2026-04</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="n">
+        <v>134</v>
+      </c>
+      <c r="N5" t="n">
+        <v>20</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
         <is>
           <t>seto77.github.io</t>
         </is>
       </c>
-      <c r="M5" t="n">
-        <v>125</v>
-      </c>
-      <c r="N5" t="n">
-        <v>18</v>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>seto77.github.io</t>
-        </is>
-      </c>
       <c r="R5" t="n">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="S5" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>link.zhihu.com</t>
+          <t>yseto.net</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>13</v>
       </c>
       <c r="D6" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1654,118 +1732,118 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
+          <t>yseto.net</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>24</v>
+      </c>
+      <c r="I6" t="n">
+        <v>17</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
           <t>link.zhihu.com</t>
         </is>
       </c>
-      <c r="H6" t="n">
-        <v>13</v>
-      </c>
-      <c r="I6" t="n">
-        <v>11</v>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>2026-04</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="n">
+        <v>94</v>
+      </c>
+      <c r="N6" t="n">
+        <v>79</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
         <is>
           <t>link.zhihu.com</t>
         </is>
       </c>
-      <c r="M6" t="n">
+      <c r="R6" t="n">
+        <v>94</v>
+      </c>
+      <c r="S6" t="n">
         <v>79</v>
-      </c>
-      <c r="N6" t="n">
-        <v>67</v>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>link.zhihu.com</t>
-        </is>
-      </c>
-      <c r="R6" t="n">
-        <v>79</v>
-      </c>
-      <c r="S6" t="n">
-        <v>67</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>seto77.github.io</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>9</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-W16</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>seto77.github.io</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>24</v>
+      </c>
+      <c r="I7" t="n">
+        <v>5</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
           <t>yseto.net</t>
         </is>
       </c>
-      <c r="C7" t="n">
-        <v>11</v>
-      </c>
-      <c r="D7" t="n">
-        <v>8</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2026-W16</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
+      <c r="M7" t="n">
+        <v>79</v>
+      </c>
+      <c r="N7" t="n">
+        <v>57</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>yseto.net</t>
         </is>
       </c>
-      <c r="H7" t="n">
-        <v>11</v>
-      </c>
-      <c r="I7" t="n">
-        <v>8</v>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>2026-04</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>yseto.net</t>
-        </is>
-      </c>
-      <c r="M7" t="n">
-        <v>66</v>
-      </c>
-      <c r="N7" t="n">
-        <v>48</v>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>yseto.net</t>
-        </is>
-      </c>
       <c r="R7" t="n">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="S7" t="n">
-        <v>48</v>
+        <v>57</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1774,7 +1852,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D8" t="n">
         <v>3</v>
@@ -1790,10 +1868,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="I8" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1806,10 +1884,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="N8" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
@@ -1822,16 +1900,16 @@
         </is>
       </c>
       <c r="R8" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="S8" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1856,10 +1934,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I9" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1872,10 +1950,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="N9" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="P9" t="inlineStr">
         <is>
@@ -1888,28 +1966,28 @@
         </is>
       </c>
       <c r="R9" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>perplexity.ai</t>
+          <t>search.brave.com</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1918,14 +1996,14 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>perplexity.ai</t>
+          <t>search.brave.com</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1938,10 +2016,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="N10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P10" t="inlineStr">
         <is>
@@ -1954,28 +2032,28 @@
         </is>
       </c>
       <c r="R10" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="S10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>search.brave.com</t>
+          <t>perplexity.ai</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1984,14 +2062,14 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>search.brave.com</t>
+          <t>perplexity.ai</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -2029,7 +2107,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2038,10 +2116,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="D12" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2095,19 +2173,19 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>github.com</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>147</v>
+        <v>34</v>
       </c>
       <c r="D13" t="n">
-        <v>72</v>
+        <v>17</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2136,10 +2214,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="N13" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="P13" t="inlineStr">
         <is>
@@ -2152,28 +2230,28 @@
         </is>
       </c>
       <c r="R13" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="S13" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>Bing</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>147</v>
+        <v>26</v>
       </c>
       <c r="D14" t="n">
-        <v>72</v>
+        <v>15</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2195,19 +2273,19 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>seto77.github.io</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>147</v>
+        <v>15</v>
       </c>
       <c r="D15" t="n">
-        <v>72</v>
+        <v>3</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2229,19 +2307,19 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>github.com</t>
+          <t>link.zhihu.com</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>41</v>
+        <v>13</v>
       </c>
       <c r="D16" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2263,19 +2341,19 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>github.com</t>
+          <t>yseto.net</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="D17" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2297,19 +2375,19 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>github.com</t>
+          <t>chatgpt.com</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="D18" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2331,19 +2409,19 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>github.com</t>
+          <t>yandex.ru</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="D19" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2365,19 +2443,19 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>seto77.github.io</t>
+          <t>perplexity.ai</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="D20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2399,19 +2477,19 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>seto77.github.io</t>
+          <t>search.brave.com</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="D21" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2438,14 +2516,14 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>seto77.github.io</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>22</v>
+        <v>152</v>
       </c>
       <c r="D22" t="n">
-        <v>3</v>
+        <v>75</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2472,14 +2550,14 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>seto77.github.io</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>22</v>
+        <v>147</v>
       </c>
       <c r="D23" t="n">
-        <v>3</v>
+        <v>72</v>
       </c>
     </row>
     <row r="24">
@@ -2490,14 +2568,14 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Bing</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>21</v>
+        <v>147</v>
       </c>
       <c r="D24" t="n">
-        <v>12</v>
+        <v>72</v>
       </c>
     </row>
     <row r="25">
@@ -2508,14 +2586,14 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Bing</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>21</v>
+        <v>147</v>
       </c>
       <c r="D25" t="n">
-        <v>12</v>
+        <v>72</v>
       </c>
     </row>
     <row r="26">
@@ -2526,14 +2604,14 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Bing</t>
+          <t>github.com</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="D26" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="27">
@@ -2544,14 +2622,14 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Bing</t>
+          <t>github.com</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="D27" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="28">
@@ -2562,14 +2640,14 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>link.zhihu.com</t>
+          <t>github.com</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="D28" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="29">
@@ -2580,14 +2658,14 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>link.zhihu.com</t>
+          <t>github.com</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="D29" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="30">
@@ -2598,14 +2676,14 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>link.zhihu.com</t>
+          <t>seto77.github.io</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="D30" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31">
@@ -2616,14 +2694,14 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>link.zhihu.com</t>
+          <t>seto77.github.io</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="D31" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32">
@@ -2634,14 +2712,14 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>yseto.net</t>
+          <t>seto77.github.io</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="D32" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="33">
@@ -2652,14 +2730,14 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>yseto.net</t>
+          <t>seto77.github.io</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="D33" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34">
@@ -2670,14 +2748,14 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>yseto.net</t>
+          <t>Bing</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="D34" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="35">
@@ -2688,14 +2766,14 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>yseto.net</t>
+          <t>Bing</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="D35" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="36">
@@ -2706,14 +2784,14 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>chatgpt.com</t>
+          <t>Bing</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="D36" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="37">
@@ -2724,14 +2802,14 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>yandex.ru</t>
+          <t>Bing</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="D37" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="38">
@@ -2742,14 +2820,14 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>chatgpt.com</t>
+          <t>link.zhihu.com</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="D38" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="39">
@@ -2760,14 +2838,14 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>yandex.ru</t>
+          <t>link.zhihu.com</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="D39" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="40">
@@ -2778,14 +2856,14 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>chatgpt.com</t>
+          <t>link.zhihu.com</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="D40" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="41">
@@ -2796,14 +2874,14 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>yandex.ru</t>
+          <t>link.zhihu.com</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D41" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="42">
@@ -2814,14 +2892,14 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>chatgpt.com</t>
+          <t>yseto.net</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D42" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="43">
@@ -2832,14 +2910,14 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>yandex.ru</t>
+          <t>yseto.net</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D43" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="44">
@@ -2850,14 +2928,14 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>search.brave.com</t>
+          <t>yseto.net</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D44" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="45">
@@ -2868,14 +2946,14 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>statics.teams.cdn.office.net</t>
+          <t>yseto.net</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D45" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="46">
@@ -2886,11 +2964,11 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>statics.teams.cdn.office.net</t>
+          <t>chatgpt.com</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D46" t="n">
         <v>3</v>
@@ -2904,14 +2982,14 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>search.brave.com</t>
+          <t>yandex.ru</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D47" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="48">
@@ -2922,11 +3000,11 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>statics.teams.cdn.office.net</t>
+          <t>chatgpt.com</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D48" t="n">
         <v>3</v>
@@ -2940,14 +3018,14 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>search.brave.com</t>
+          <t>yandex.ru</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D49" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="50">
@@ -2958,11 +3036,11 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>statics.teams.cdn.office.net</t>
+          <t>chatgpt.com</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D50" t="n">
         <v>3</v>
@@ -2976,193 +3054,373 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>search.brave.com</t>
+          <t>yandex.ru</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D51" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>chatgpt.com</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>145</v>
+        <v>5</v>
       </c>
       <c r="D52" t="n">
-        <v>71</v>
+        <v>3</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>github.com</t>
+          <t>yandex.ru</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>41</v>
+        <v>5</v>
       </c>
       <c r="D53" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>seto77.github.io</t>
+          <t>search.brave.com</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="D54" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Bing</t>
+          <t>statics.teams.cdn.office.net</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="D55" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Baidu</t>
+          <t>statics.teams.cdn.office.net</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="D56" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>link.zhihu.com</t>
+          <t>search.brave.com</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D57" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>yseto.net</t>
+          <t>statics.teams.cdn.office.net</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D58" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>yandex.ru</t>
+          <t>search.brave.com</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D59" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>search.brave.com</t>
+          <t>statics.teams.cdn.office.net</t>
         </is>
       </c>
       <c r="C60" t="n">
         <v>4</v>
       </c>
       <c r="D60" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>statics.teams.cdn.office.net</t>
+          <t>search.brave.com</t>
         </is>
       </c>
       <c r="C61" t="n">
         <v>4</v>
       </c>
       <c r="D61" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>145</v>
+      </c>
+      <c r="D62" t="n">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>github.com</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>41</v>
+      </c>
+      <c r="D63" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>seto77.github.io</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>22</v>
+      </c>
+      <c r="D64" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Bing</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>21</v>
+      </c>
+      <c r="D65" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Baidu</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>16</v>
+      </c>
+      <c r="D66" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>link.zhihu.com</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>11</v>
+      </c>
+      <c r="D67" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>yseto.net</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>10</v>
+      </c>
+      <c r="D68" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>yandex.ru</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>5</v>
+      </c>
+      <c r="D69" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>search.brave.com</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>4</v>
+      </c>
+      <c r="D70" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>statics.teams.cdn.office.net</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>4</v>
+      </c>
+      <c r="D71" t="n">
         <v>3</v>
       </c>
     </row>
@@ -3177,7 +3435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W61"/>
+  <dimension ref="A1:W71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3203,102 +3461,102 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="8" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Date Collected</t>
         </is>
       </c>
-      <c r="B1" s="8" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Path</t>
         </is>
       </c>
-      <c r="C1" s="8" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="D1" s="8" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Total Count</t>
         </is>
       </c>
-      <c r="E1" s="8" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Unique</t>
         </is>
       </c>
-      <c r="G1" s="8" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Period</t>
         </is>
       </c>
-      <c r="H1" s="8" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Path</t>
         </is>
       </c>
-      <c r="I1" s="8" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="J1" s="8" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Total Count</t>
         </is>
       </c>
-      <c r="K1" s="8" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Unique</t>
         </is>
       </c>
-      <c r="M1" s="8" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Period</t>
         </is>
       </c>
-      <c r="N1" s="8" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Path</t>
         </is>
       </c>
-      <c r="O1" s="8" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="P1" s="8" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Total Count</t>
         </is>
       </c>
-      <c r="Q1" s="8" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Unique</t>
         </is>
       </c>
-      <c r="S1" s="8" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Period</t>
         </is>
       </c>
-      <c r="T1" s="8" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Path</t>
         </is>
       </c>
-      <c r="U1" s="8" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="V1" s="8" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Total Count</t>
         </is>
       </c>
-      <c r="W1" s="8" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Unique</t>
         </is>
@@ -3307,7 +3565,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -3321,10 +3579,10 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="E2" t="n">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -3342,10 +3600,10 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>246</v>
+        <v>486</v>
       </c>
       <c r="K2" t="n">
-        <v>151</v>
+        <v>305</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -3363,10 +3621,10 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1492</v>
+        <v>1732</v>
       </c>
       <c r="Q2" t="n">
-        <v>889</v>
+        <v>1043</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -3384,16 +3642,16 @@
         </is>
       </c>
       <c r="V2" t="n">
-        <v>1492</v>
+        <v>1732</v>
       </c>
       <c r="W2" t="n">
-        <v>889</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -3407,10 +3665,10 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>201</v>
+        <v>226</v>
       </c>
       <c r="E3" t="n">
-        <v>130</v>
+        <v>146</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -3428,10 +3686,10 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>201</v>
+        <v>427</v>
       </c>
       <c r="K3" t="n">
-        <v>130</v>
+        <v>276</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -3449,10 +3707,10 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>969</v>
+        <v>1195</v>
       </c>
       <c r="Q3" t="n">
-        <v>630</v>
+        <v>776</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -3470,102 +3728,102 @@
         </is>
       </c>
       <c r="V3" t="n">
-        <v>969</v>
+        <v>1195</v>
       </c>
       <c r="W3" t="n">
-        <v>630</v>
+        <v>776</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>/seto77/ReciPro/releases/tag/v.4.924</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>/releases/tag/v.4.924</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>90</v>
+      </c>
+      <c r="E4" t="n">
+        <v>45</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2026-W16</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
           <t>/seto77/ReciPro/releases/tag/v.4.921</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>/releases/tag/v.4.921</t>
         </is>
       </c>
-      <c r="D4" t="n">
-        <v>83</v>
-      </c>
-      <c r="E4" t="n">
-        <v>49</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>2026-W16</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
+      <c r="J4" t="n">
+        <v>139</v>
+      </c>
+      <c r="K4" t="n">
+        <v>82</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
         <is>
           <t>/seto77/ReciPro/releases/tag/v.4.921</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>/releases/tag/v.4.921</t>
         </is>
       </c>
-      <c r="J4" t="n">
-        <v>83</v>
-      </c>
-      <c r="K4" t="n">
-        <v>49</v>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>2026-04</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
+      <c r="P4" t="n">
+        <v>553</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>327</v>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
         <is>
           <t>/seto77/ReciPro/releases/tag/v.4.921</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>/releases/tag/v.4.921</t>
         </is>
       </c>
-      <c r="P4" t="n">
-        <v>497</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>294</v>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>/seto77/ReciPro/releases/tag/v.4.921</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>/releases/tag/v.4.921</t>
-        </is>
-      </c>
       <c r="V4" t="n">
-        <v>497</v>
+        <v>553</v>
       </c>
       <c r="W4" t="n">
-        <v>294</v>
+        <v>327</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -3579,10 +3837,10 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="E5" t="n">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -3600,10 +3858,10 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>56</v>
+        <v>124</v>
       </c>
       <c r="K5" t="n">
-        <v>29</v>
+        <v>66</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -3612,19 +3870,19 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>/seto77/ReciPro/releases/tag/v.4.919</t>
+          <t>/seto77/ReciPro/releases</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>/releases/tag/v.4.919</t>
+          <t>/releases</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>311</v>
+        <v>371</v>
       </c>
       <c r="Q5" t="n">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -3633,42 +3891,42 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>/seto77/ReciPro/releases/tag/v.4.919</t>
+          <t>/seto77/ReciPro/releases</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>/releases/tag/v.4.919</t>
+          <t>/releases</t>
         </is>
       </c>
       <c r="V5" t="n">
-        <v>311</v>
+        <v>371</v>
       </c>
       <c r="W5" t="n">
-        <v>199</v>
+        <v>196</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>/seto77/ReciPro/wiki</t>
+          <t>/seto77/ReciPro/releases/tag/v.4.921</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>/wiki</t>
+          <t>/releases/tag/v.4.921</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="E6" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -3677,19 +3935,19 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>/seto77/ReciPro/wiki</t>
+          <t>/seto77/ReciPro/releases/tag/v.4.924</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>/wiki</t>
+          <t>/releases/tag/v.4.924</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>36</v>
+        <v>90</v>
       </c>
       <c r="K6" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -3698,19 +3956,19 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>/seto77/ReciPro/releases</t>
+          <t>/seto77/ReciPro/releases/tag/v.4.919</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>/releases</t>
+          <t>/releases/tag/v.4.919</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="Q6" t="n">
-        <v>159</v>
+        <v>199</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -3719,42 +3977,42 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>/seto77/ReciPro/releases</t>
+          <t>/seto77/ReciPro/releases/tag/v.4.919</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>/releases</t>
+          <t>/releases/tag/v.4.919</t>
         </is>
       </c>
       <c r="V6" t="n">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="W6" t="n">
-        <v>159</v>
+        <v>199</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>/seto77/ReciPro/issues</t>
+          <t>/seto77/ReciPro/wiki</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>/issues</t>
+          <t>/wiki</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="E7" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -3763,19 +4021,19 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>/seto77/ReciPro/issues</t>
+          <t>/seto77/ReciPro/wiki</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>/issues</t>
+          <t>/wiki</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>25</v>
+        <v>71</v>
       </c>
       <c r="K7" t="n">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -3793,10 +4051,10 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>213</v>
+        <v>248</v>
       </c>
       <c r="Q7" t="n">
-        <v>168</v>
+        <v>198</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -3814,33 +4072,33 @@
         </is>
       </c>
       <c r="V7" t="n">
-        <v>213</v>
+        <v>248</v>
       </c>
       <c r="W7" t="n">
-        <v>168</v>
+        <v>198</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>/seto77/ReciPro/releases/tag/v.4.919</t>
+          <t>/seto77/ReciPro/issues</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>/releases/tag/v.4.919</t>
+          <t>/issues</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E8" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -3849,19 +4107,19 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>/seto77/ReciPro/releases/tag/v.4.919</t>
+          <t>/seto77/ReciPro/issues</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>/releases/tag/v.4.919</t>
+          <t>/issues</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>21</v>
+        <v>49</v>
       </c>
       <c r="K8" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -3879,10 +4137,10 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>150</v>
+        <v>174</v>
       </c>
       <c r="Q8" t="n">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -3900,33 +4158,33 @@
         </is>
       </c>
       <c r="V8" t="n">
-        <v>150</v>
+        <v>174</v>
       </c>
       <c r="W8" t="n">
-        <v>71</v>
+        <v>84</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>/seto77/ReciPro/tree/master/ReciPro</t>
+          <t>/seto77/ReciPro/blob/master/README.md</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>/tree/master/ReciPro</t>
+          <t>/blob/master/README.md</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>14</v>
       </c>
       <c r="E9" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -3935,19 +4193,19 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>/seto77/ReciPro/tree/master/ReciPro</t>
+          <t>/seto77/ReciPro/blob/master/README.md</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>/tree/master/ReciPro</t>
+          <t>/blob/master/README.md</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="K9" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -3965,10 +4223,10 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="Q9" t="n">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -3986,30 +4244,30 @@
         </is>
       </c>
       <c r="V9" t="n">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="W9" t="n">
-        <v>64</v>
+        <v>75</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>/seto77/ReciPro/blob/master/README.md</t>
+          <t>/seto77/ReciPro/tree/master/ReciProSetup</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>/blob/master/README.md</t>
+          <t>/tree/master/ReciProSetup</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E10" t="n">
         <v>10</v>
@@ -4021,19 +4279,19 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>/seto77/ReciPro/blob/master/README.md</t>
+          <t>/seto77/ReciPro/tree/master/ReciPro</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>/blob/master/README.md</t>
+          <t>/tree/master/ReciPro</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="K10" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -4042,19 +4300,19 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>/seto77/ReciPro/tree/master/ReciPro</t>
+          <t>/seto77/ReciPro/releases/tag/v.4.924</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>/tree/master/ReciPro</t>
+          <t>/releases/tag/v.4.924</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="Q10" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -4063,42 +4321,42 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>/seto77/ReciPro/tree/master/ReciPro</t>
+          <t>/seto77/ReciPro/releases/tag/v.4.924</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>/tree/master/ReciPro</t>
+          <t>/releases/tag/v.4.924</t>
         </is>
       </c>
       <c r="V10" t="n">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="W10" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>/seto77/ReciPro/releases/tag/v.4.904</t>
+          <t>/seto77/ReciPro/tree/master/ReciPro</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>/releases/tag/v.4.904</t>
+          <t>/tree/master/ReciPro</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -4107,19 +4365,19 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>/seto77/ReciPro/releases/tag/v.4.904</t>
+          <t>/seto77/ReciPro/releases/tag/v.4.919</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>/releases/tag/v.4.904</t>
+          <t>/releases/tag/v.4.919</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -4128,19 +4386,19 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>/seto77/ReciPro/tree/master</t>
+          <t>/seto77/ReciPro/tree/master/ReciPro</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>/tree/master</t>
+          <t>/tree/master/ReciPro</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>40</v>
+        <v>88</v>
       </c>
       <c r="Q11" t="n">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -4149,25 +4407,25 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>/seto77/ReciPro/tree/master</t>
+          <t>/seto77/ReciPro/tree/master/ReciPro</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>/tree/master</t>
+          <t>/tree/master/ReciPro</t>
         </is>
       </c>
       <c r="V11" t="n">
-        <v>40</v>
+        <v>88</v>
       </c>
       <c r="W11" t="n">
-        <v>28</v>
+        <v>49</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -4181,31 +4439,31 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="E12" t="n">
         <v>151</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-W15</t>
+          <t>2026-W16</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>/seto77/ReciPro</t>
+          <t>/seto77/ReciPro/tree/master/ReciProSetup</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Overview</t>
+          <t>/tree/master/ReciProSetup</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>1246</v>
+        <v>12</v>
       </c>
       <c r="K12" t="n">
-        <v>738</v>
+        <v>10</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -4214,19 +4472,19 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>/seto77/ReciPro/releases/tag/v.4.904</t>
+          <t>/seto77/ReciPro/tree/master</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>/releases/tag/v.4.904</t>
+          <t>/tree/master</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="Q12" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -4235,130 +4493,214 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>/seto77/ReciPro/releases/tag/v.4.904</t>
+          <t>/seto77/ReciPro/tree/master</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>/releases/tag/v.4.904</t>
+          <t>/tree/master</t>
         </is>
       </c>
       <c r="V12" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="W12" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>/seto77/ReciPro</t>
+          <t>/seto77/ReciPro/releases/tag/v.4.923</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Overview</t>
+          <t>/releases/tag/v.4.923</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>253</v>
+        <v>201</v>
       </c>
       <c r="E13" t="n">
-        <v>151</v>
+        <v>130</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-W15</t>
+          <t>2026-W16</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>/seto77/ReciPro/releases/tag/v.4.923</t>
+          <t>/seto77/ReciPro/releases/tag/v.4.904</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>/releases/tag/v.4.923</t>
+          <t>/releases/tag/v.4.904</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>768</v>
+        <v>10</v>
       </c>
       <c r="K13" t="n">
-        <v>500</v>
+        <v>1</v>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>/seto77/ReciPro/releases/tag/v.4.904</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>/releases/tag/v.4.904</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>/seto77/ReciPro/releases/tag/v.4.904</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>/releases/tag/v.4.904</t>
+        </is>
+      </c>
+      <c r="V13" t="n">
+        <v>20</v>
+      </c>
+      <c r="W13" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
+          <t>/seto77/ReciPro/releases/tag/v.4.921</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>/releases/tag/v.4.921</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>83</v>
+      </c>
+      <c r="E14" t="n">
+        <v>49</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>2026-W15</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
           <t>/seto77/ReciPro</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>Overview</t>
         </is>
       </c>
-      <c r="D14" t="n">
-        <v>253</v>
-      </c>
-      <c r="E14" t="n">
-        <v>151</v>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>2026-W15</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>/seto77/ReciPro/releases/tag/v.4.921</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>/releases/tag/v.4.921</t>
-        </is>
-      </c>
       <c r="J14" t="n">
-        <v>414</v>
+        <v>1246</v>
       </c>
       <c r="K14" t="n">
-        <v>245</v>
+        <v>738</v>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>/seto77/ReciPro/tree/master/ReciProSetup</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>/tree/master/ReciProSetup</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>10</v>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>/seto77/ReciPro/tree/master/ReciProSetup</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>/tree/master/ReciProSetup</t>
+        </is>
+      </c>
+      <c r="V14" t="n">
+        <v>12</v>
+      </c>
+      <c r="W14" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>/seto77/ReciPro</t>
+          <t>/seto77/ReciPro/releases</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Overview</t>
+          <t>/releases</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>249</v>
+        <v>56</v>
       </c>
       <c r="E15" t="n">
-        <v>148</v>
+        <v>29</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -4367,42 +4709,42 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>/seto77/ReciPro/releases/tag/v.4.919</t>
+          <t>/seto77/ReciPro/releases/tag/v.4.923</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>/releases/tag/v.4.919</t>
+          <t>/releases/tag/v.4.923</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>290</v>
+        <v>768</v>
       </c>
       <c r="K15" t="n">
-        <v>185</v>
+        <v>500</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>/seto77/ReciPro/releases/tag/v.4.923</t>
+          <t>/seto77/ReciPro/wiki</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>/releases/tag/v.4.923</t>
+          <t>/wiki</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>166</v>
+        <v>36</v>
       </c>
       <c r="E16" t="n">
-        <v>108</v>
+        <v>30</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -4411,42 +4753,42 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>/seto77/ReciPro/releases</t>
+          <t>/seto77/ReciPro/releases/tag/v.4.921</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>/releases</t>
+          <t>/releases/tag/v.4.921</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>247</v>
+        <v>414</v>
       </c>
       <c r="K16" t="n">
-        <v>130</v>
+        <v>245</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>/seto77/ReciPro/releases/tag/v.4.923</t>
+          <t>/seto77/ReciPro/issues</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>/releases/tag/v.4.923</t>
+          <t>/issues</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>166</v>
+        <v>25</v>
       </c>
       <c r="E17" t="n">
-        <v>108</v>
+        <v>12</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -4455,42 +4797,42 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>/seto77/ReciPro/wiki</t>
+          <t>/seto77/ReciPro/releases/tag/v.4.919</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>/wiki</t>
+          <t>/releases/tag/v.4.919</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>177</v>
+        <v>290</v>
       </c>
       <c r="K17" t="n">
-        <v>138</v>
+        <v>185</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>/seto77/ReciPro/releases/tag/v.4.923</t>
+          <t>/seto77/ReciPro/releases/tag/v.4.919</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>/releases/tag/v.4.923</t>
+          <t>/releases/tag/v.4.919</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>166</v>
+        <v>21</v>
       </c>
       <c r="E18" t="n">
-        <v>108</v>
+        <v>14</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -4499,42 +4841,42 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>/seto77/ReciPro/issues</t>
+          <t>/seto77/ReciPro/releases</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>/issues</t>
+          <t>/releases</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>125</v>
+        <v>247</v>
       </c>
       <c r="K18" t="n">
-        <v>59</v>
+        <v>130</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>/seto77/ReciPro/releases/tag/v.4.923</t>
+          <t>/seto77/ReciPro/tree/master/ReciPro</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>/releases/tag/v.4.923</t>
+          <t>/tree/master/ReciPro</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>153</v>
+        <v>14</v>
       </c>
       <c r="E19" t="n">
-        <v>99</v>
+        <v>8</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -4543,42 +4885,42 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>/seto77/ReciPro/blob/master/README.md</t>
+          <t>/seto77/ReciPro/wiki</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>/blob/master/README.md</t>
+          <t>/wiki</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>67</v>
+        <v>177</v>
       </c>
       <c r="K19" t="n">
-        <v>54</v>
+        <v>138</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>/seto77/ReciPro/releases/tag/v.4.921</t>
+          <t>/seto77/ReciPro/blob/master/README.md</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>/releases/tag/v.4.921</t>
+          <t>/blob/master/README.md</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>83</v>
+        <v>13</v>
       </c>
       <c r="E20" t="n">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -4587,42 +4929,42 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>/seto77/ReciPro/tree/master/ReciPro</t>
+          <t>/seto77/ReciPro/issues</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>/tree/master/ReciPro</t>
+          <t>/issues</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>62</v>
+        <v>125</v>
       </c>
       <c r="K20" t="n">
-        <v>32</v>
+        <v>59</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>/seto77/ReciPro/releases/tag/v.4.921</t>
+          <t>/seto77/ReciPro/releases/tag/v.4.904</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>/releases/tag/v.4.921</t>
+          <t>/releases/tag/v.4.904</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>83</v>
+        <v>10</v>
       </c>
       <c r="E21" t="n">
-        <v>49</v>
+        <v>1</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -4631,19 +4973,19 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>/seto77/ReciPro/tree/master</t>
+          <t>/seto77/ReciPro/blob/master/README.md</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>/tree/master</t>
+          <t>/blob/master/README.md</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>40</v>
+        <v>67</v>
       </c>
       <c r="K21" t="n">
-        <v>28</v>
+        <v>54</v>
       </c>
     </row>
     <row r="22">
@@ -4654,19 +4996,19 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>/seto77/ReciPro/releases/tag/v.4.921</t>
+          <t>/seto77/ReciPro</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>/releases/tag/v.4.921</t>
+          <t>Overview</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>83</v>
+        <v>253</v>
       </c>
       <c r="E22" t="n">
-        <v>49</v>
+        <v>151</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -4675,19 +5017,19 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>/seto77/ReciPro/releases/tag/v.4.904</t>
+          <t>/seto77/ReciPro/tree/master/ReciPro</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>/releases/tag/v.4.904</t>
+          <t>/tree/master/ReciPro</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>10</v>
+        <v>62</v>
       </c>
       <c r="K22" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
     </row>
     <row r="23">
@@ -4698,19 +5040,40 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>/seto77/ReciPro/releases/tag/v.4.921</t>
+          <t>/seto77/ReciPro</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>/releases/tag/v.4.921</t>
+          <t>Overview</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>83</v>
+        <v>253</v>
       </c>
       <c r="E23" t="n">
-        <v>49</v>
+        <v>151</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>2026-W15</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>/seto77/ReciPro/tree/master</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>/tree/master</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>40</v>
+      </c>
+      <c r="K23" t="n">
+        <v>28</v>
       </c>
     </row>
     <row r="24">
@@ -4721,19 +5084,40 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>/seto77/ReciPro/releases/tag/v.4.919</t>
+          <t>/seto77/ReciPro</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>/releases/tag/v.4.919</t>
+          <t>Overview</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>61</v>
+        <v>253</v>
       </c>
       <c r="E24" t="n">
-        <v>36</v>
+        <v>151</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>2026-W15</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>/seto77/ReciPro/releases/tag/v.4.904</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>/releases/tag/v.4.904</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>10</v>
+      </c>
+      <c r="K24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -4744,19 +5128,19 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>/seto77/ReciPro/releases/tag/v.4.919</t>
+          <t>/seto77/ReciPro</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>/releases/tag/v.4.919</t>
+          <t>Overview</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>49</v>
+        <v>249</v>
       </c>
       <c r="E25" t="n">
-        <v>32</v>
+        <v>148</v>
       </c>
     </row>
     <row r="26">
@@ -4767,19 +5151,19 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>/seto77/ReciPro/releases</t>
+          <t>/seto77/ReciPro/releases/tag/v.4.923</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>/releases</t>
+          <t>/releases/tag/v.4.923</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>49</v>
+        <v>166</v>
       </c>
       <c r="E26" t="n">
-        <v>26</v>
+        <v>108</v>
       </c>
     </row>
     <row r="27">
@@ -4790,19 +5174,19 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>/seto77/ReciPro/releases/tag/v.4.919</t>
+          <t>/seto77/ReciPro/releases/tag/v.4.923</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>/releases/tag/v.4.919</t>
+          <t>/releases/tag/v.4.923</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>49</v>
+        <v>166</v>
       </c>
       <c r="E27" t="n">
-        <v>32</v>
+        <v>108</v>
       </c>
     </row>
     <row r="28">
@@ -4813,19 +5197,19 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>/seto77/ReciPro/releases</t>
+          <t>/seto77/ReciPro/releases/tag/v.4.923</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>/releases</t>
+          <t>/releases/tag/v.4.923</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>49</v>
+        <v>166</v>
       </c>
       <c r="E28" t="n">
-        <v>26</v>
+        <v>108</v>
       </c>
     </row>
     <row r="29">
@@ -4836,19 +5220,19 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>/seto77/ReciPro/releases/tag/v.4.919</t>
+          <t>/seto77/ReciPro/releases/tag/v.4.923</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>/releases/tag/v.4.919</t>
+          <t>/releases/tag/v.4.923</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>49</v>
+        <v>153</v>
       </c>
       <c r="E29" t="n">
-        <v>32</v>
+        <v>99</v>
       </c>
     </row>
     <row r="30">
@@ -4859,19 +5243,19 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>/seto77/ReciPro/releases</t>
+          <t>/seto77/ReciPro/releases/tag/v.4.921</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>/releases</t>
+          <t>/releases/tag/v.4.921</t>
         </is>
       </c>
       <c r="D30" t="n">
+        <v>83</v>
+      </c>
+      <c r="E30" t="n">
         <v>49</v>
-      </c>
-      <c r="E30" t="n">
-        <v>26</v>
       </c>
     </row>
     <row r="31">
@@ -4882,19 +5266,19 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>/seto77/ReciPro/releases</t>
+          <t>/seto77/ReciPro/releases/tag/v.4.921</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>/releases</t>
+          <t>/releases/tag/v.4.921</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="E31" t="n">
-        <v>25</v>
+        <v>49</v>
       </c>
     </row>
     <row r="32">
@@ -4905,19 +5289,19 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>/seto77/ReciPro/wiki</t>
+          <t>/seto77/ReciPro/releases/tag/v.4.921</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>/wiki</t>
+          <t>/releases/tag/v.4.921</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>36</v>
+        <v>83</v>
       </c>
       <c r="E32" t="n">
-        <v>28</v>
+        <v>49</v>
       </c>
     </row>
     <row r="33">
@@ -4928,19 +5312,19 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>/seto77/ReciPro/wiki</t>
+          <t>/seto77/ReciPro/releases/tag/v.4.921</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>/wiki</t>
+          <t>/releases/tag/v.4.921</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>36</v>
+        <v>83</v>
       </c>
       <c r="E33" t="n">
-        <v>28</v>
+        <v>49</v>
       </c>
     </row>
     <row r="34">
@@ -4951,19 +5335,19 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>/seto77/ReciPro/wiki</t>
+          <t>/seto77/ReciPro/releases/tag/v.4.919</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>/wiki</t>
+          <t>/releases/tag/v.4.919</t>
         </is>
       </c>
       <c r="D34" t="n">
+        <v>61</v>
+      </c>
+      <c r="E34" t="n">
         <v>36</v>
-      </c>
-      <c r="E34" t="n">
-        <v>28</v>
       </c>
     </row>
     <row r="35">
@@ -4974,19 +5358,19 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>/seto77/ReciPro/wiki</t>
+          <t>/seto77/ReciPro/releases/tag/v.4.919</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>/wiki</t>
+          <t>/releases/tag/v.4.919</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="E35" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="36">
@@ -4997,19 +5381,19 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>/seto77/ReciPro/issues</t>
+          <t>/seto77/ReciPro/releases</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>/issues</t>
+          <t>/releases</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="E36" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="37">
@@ -5020,19 +5404,19 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>/seto77/ReciPro/issues</t>
+          <t>/seto77/ReciPro/releases/tag/v.4.919</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>/issues</t>
+          <t>/releases/tag/v.4.919</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="E37" t="n">
-        <v>12</v>
+        <v>32</v>
       </c>
     </row>
     <row r="38">
@@ -5043,19 +5427,19 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>/seto77/ReciPro/issues</t>
+          <t>/seto77/ReciPro/releases</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>/issues</t>
+          <t>/releases</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="E38" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="39">
@@ -5066,19 +5450,19 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>/seto77/ReciPro/issues</t>
+          <t>/seto77/ReciPro/releases/tag/v.4.919</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>/issues</t>
+          <t>/releases/tag/v.4.919</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="E39" t="n">
-        <v>11</v>
+        <v>32</v>
       </c>
     </row>
     <row r="40">
@@ -5089,19 +5473,19 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>/seto77/ReciPro/blob/master/README.md</t>
+          <t>/seto77/ReciPro/releases</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>/blob/master/README.md</t>
+          <t>/releases</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>15</v>
+        <v>49</v>
       </c>
       <c r="E40" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="41">
@@ -5112,19 +5496,19 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>/seto77/ReciPro/blob/master/README.md</t>
+          <t>/seto77/ReciPro/releases</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>/blob/master/README.md</t>
+          <t>/releases</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>14</v>
+        <v>48</v>
       </c>
       <c r="E41" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
     </row>
     <row r="42">
@@ -5135,19 +5519,19 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>/seto77/ReciPro/blob/master/README.md</t>
+          <t>/seto77/ReciPro/wiki</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>/blob/master/README.md</t>
+          <t>/wiki</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="E42" t="n">
-        <v>11</v>
+        <v>28</v>
       </c>
     </row>
     <row r="43">
@@ -5158,19 +5542,19 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>/seto77/ReciPro/blob/master/README.md</t>
+          <t>/seto77/ReciPro/wiki</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>/blob/master/README.md</t>
+          <t>/wiki</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="E43" t="n">
-        <v>11</v>
+        <v>28</v>
       </c>
     </row>
     <row r="44">
@@ -5181,19 +5565,19 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>/seto77/ReciPro/tree/master/ReciPro</t>
+          <t>/seto77/ReciPro/wiki</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>/tree/master/ReciPro</t>
+          <t>/wiki</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="E44" t="n">
-        <v>6</v>
+        <v>28</v>
       </c>
     </row>
     <row r="45">
@@ -5204,19 +5588,19 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>/seto77/ReciPro/tree/master/ReciPro</t>
+          <t>/seto77/ReciPro/wiki</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>/tree/master/ReciPro</t>
+          <t>/wiki</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="E45" t="n">
-        <v>6</v>
+        <v>28</v>
       </c>
     </row>
     <row r="46">
@@ -5227,19 +5611,19 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>/seto77/ReciPro/tree/master/ReciPro</t>
+          <t>/seto77/ReciPro/issues</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>/tree/master/ReciPro</t>
+          <t>/issues</t>
         </is>
       </c>
       <c r="D46" t="n">
+        <v>25</v>
+      </c>
+      <c r="E46" t="n">
         <v>12</v>
-      </c>
-      <c r="E46" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="47">
@@ -5250,19 +5634,19 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>/seto77/ReciPro/tree/master/ReciPro</t>
+          <t>/seto77/ReciPro/issues</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>/tree/master/ReciPro</t>
+          <t>/issues</t>
         </is>
       </c>
       <c r="D47" t="n">
+        <v>25</v>
+      </c>
+      <c r="E47" t="n">
         <v>12</v>
-      </c>
-      <c r="E47" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="48">
@@ -5273,19 +5657,19 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>/seto77/ReciPro/tree/master</t>
+          <t>/seto77/ReciPro/issues</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>/tree/master</t>
+          <t>/issues</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="E48" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="49">
@@ -5296,19 +5680,19 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>/seto77/ReciPro/tree/master</t>
+          <t>/seto77/ReciPro/issues</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>/tree/master</t>
+          <t>/issues</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="E49" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="50">
@@ -5319,19 +5703,19 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>/seto77/ReciPro/tree/master</t>
+          <t>/seto77/ReciPro/blob/master/README.md</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>/tree/master</t>
+          <t>/blob/master/README.md</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E50" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="51">
@@ -5342,248 +5726,478 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>/seto77/ReciPro/tree/master</t>
+          <t>/seto77/ReciPro/blob/master/README.md</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>/tree/master</t>
+          <t>/blob/master/README.md</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E51" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>/seto77/ReciPro</t>
+          <t>/seto77/ReciPro/blob/master/README.md</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Overview</t>
+          <t>/blob/master/README.md</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>238</v>
+        <v>14</v>
       </c>
       <c r="E52" t="n">
-        <v>137</v>
+        <v>11</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>/seto77/ReciPro/releases/tag/v.4.923</t>
+          <t>/seto77/ReciPro/blob/master/README.md</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>/releases/tag/v.4.923</t>
+          <t>/blob/master/README.md</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>117</v>
+        <v>14</v>
       </c>
       <c r="E53" t="n">
-        <v>77</v>
+        <v>11</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>/seto77/ReciPro/releases/tag/v.4.919</t>
+          <t>/seto77/ReciPro/tree/master/ReciPro</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>/releases/tag/v.4.919</t>
+          <t>/tree/master/ReciPro</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>82</v>
+        <v>12</v>
       </c>
       <c r="E54" t="n">
-        <v>53</v>
+        <v>6</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>/seto77/ReciPro/releases/tag/v.4.921</t>
+          <t>/seto77/ReciPro/tree/master/ReciPro</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>/releases/tag/v.4.921</t>
+          <t>/tree/master/ReciPro</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>82</v>
+        <v>12</v>
       </c>
       <c r="E55" t="n">
-        <v>49</v>
+        <v>6</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>/seto77/ReciPro/releases</t>
+          <t>/seto77/ReciPro/tree/master/ReciPro</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>/releases</t>
+          <t>/tree/master/ReciPro</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>52</v>
+        <v>12</v>
       </c>
       <c r="E56" t="n">
-        <v>27</v>
+        <v>6</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>/seto77/ReciPro/wiki</t>
+          <t>/seto77/ReciPro/tree/master/ReciPro</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>/wiki</t>
+          <t>/tree/master/ReciPro</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="E57" t="n">
-        <v>26</v>
+        <v>6</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>/seto77/ReciPro/issues</t>
+          <t>/seto77/ReciPro/tree/master</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>/issues</t>
+          <t>/tree/master</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="E58" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>/seto77/ReciPro/tree/master/ReciPro</t>
+          <t>/seto77/ReciPro/tree/master</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>/tree/master/ReciPro</t>
+          <t>/tree/master</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E59" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>/seto77/ReciPro/blob/master/README.md</t>
+          <t>/seto77/ReciPro/tree/master</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>/blob/master/README.md</t>
+          <t>/tree/master</t>
         </is>
       </c>
       <c r="D60" t="n">
         <v>10</v>
       </c>
       <c r="E60" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>/seto77/ReciPro/releases/tag/v.4.904</t>
+          <t>/seto77/ReciPro/tree/master</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>/releases/tag/v.4.904</t>
+          <t>/tree/master</t>
         </is>
       </c>
       <c r="D61" t="n">
         <v>10</v>
       </c>
       <c r="E61" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>/seto77/ReciPro</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Overview</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>238</v>
+      </c>
+      <c r="E62" t="n">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>/seto77/ReciPro/releases/tag/v.4.923</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>/releases/tag/v.4.923</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>117</v>
+      </c>
+      <c r="E63" t="n">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>/seto77/ReciPro/releases/tag/v.4.919</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>/releases/tag/v.4.919</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>82</v>
+      </c>
+      <c r="E64" t="n">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>/seto77/ReciPro/releases/tag/v.4.921</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>/releases/tag/v.4.921</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>82</v>
+      </c>
+      <c r="E65" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>/seto77/ReciPro/releases</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>/releases</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>52</v>
+      </c>
+      <c r="E66" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>/seto77/ReciPro/wiki</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>/wiki</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>33</v>
+      </c>
+      <c r="E67" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>/seto77/ReciPro/issues</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>/issues</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>26</v>
+      </c>
+      <c r="E68" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>/seto77/ReciPro/tree/master/ReciPro</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>/tree/master/ReciPro</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>14</v>
+      </c>
+      <c r="E69" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>/seto77/ReciPro/blob/master/README.md</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>/blob/master/README.md</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>10</v>
+      </c>
+      <c r="E70" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>/seto77/ReciPro/releases/tag/v.4.904</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>/releases/tag/v.4.904</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>10</v>
+      </c>
+      <c r="E71" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5613,22 +6227,22 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="8" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Release Tag</t>
         </is>
       </c>
-      <c r="B1" s="8" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Release Date</t>
         </is>
       </c>
-      <c r="C1" s="8" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Asset Name</t>
         </is>
       </c>
-      <c r="D1" s="8" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Download Count</t>
         </is>
@@ -5651,7 +6265,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>142</v>
       </c>
     </row>
     <row r="3">
@@ -5671,7 +6285,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="4">
@@ -5791,7 +6405,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>753</v>
+        <v>758</v>
       </c>
     </row>
     <row r="10">
@@ -8375,13 +8989,13 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="inlineStr">
+      <c r="A139" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="D139" s="1" t="n">
-        <v>27522</v>
+      <c r="D139" t="n">
+        <v>27668</v>
       </c>
     </row>
   </sheetData>
@@ -8395,7 +9009,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W4"/>
+  <dimension ref="A1:W5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8421,102 +9035,102 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="8" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B1" s="8" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Stars</t>
         </is>
       </c>
-      <c r="C1" s="8" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Forks</t>
         </is>
       </c>
-      <c r="D1" s="8" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Open Issues</t>
         </is>
       </c>
-      <c r="E1" s="8" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Watchers</t>
         </is>
       </c>
-      <c r="G1" s="8" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Period</t>
         </is>
       </c>
-      <c r="H1" s="8" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Stars</t>
         </is>
       </c>
-      <c r="I1" s="8" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Forks</t>
         </is>
       </c>
-      <c r="J1" s="8" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Open Issues</t>
         </is>
       </c>
-      <c r="K1" s="8" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Watchers</t>
         </is>
       </c>
-      <c r="M1" s="8" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Period</t>
         </is>
       </c>
-      <c r="N1" s="8" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Stars</t>
         </is>
       </c>
-      <c r="O1" s="8" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Forks</t>
         </is>
       </c>
-      <c r="P1" s="8" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Open Issues</t>
         </is>
       </c>
-      <c r="Q1" s="8" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Watchers</t>
         </is>
       </c>
-      <c r="S1" s="8" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Period</t>
         </is>
       </c>
-      <c r="T1" s="8" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Stars</t>
         </is>
       </c>
-      <c r="U1" s="8" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Forks</t>
         </is>
       </c>
-      <c r="V1" s="8" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Open Issues</t>
         </is>
       </c>
-      <c r="W1" s="8" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Watchers</t>
         </is>
@@ -8525,11 +9139,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C2" t="n">
         <v>13</v>
@@ -8538,7 +9152,7 @@
         <v>34</v>
       </c>
       <c r="E2" t="n">
-        <v>162</v>
+        <v>7</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -8546,7 +9160,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="I2" t="n">
         <v>13</v>
@@ -8555,7 +9169,7 @@
         <v>34</v>
       </c>
       <c r="K2" t="n">
-        <v>162</v>
+        <v>7</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -8563,7 +9177,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O2" t="n">
         <v>13</v>
@@ -8572,7 +9186,7 @@
         <v>34</v>
       </c>
       <c r="Q2" t="n">
-        <v>162</v>
+        <v>7</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -8580,7 +9194,7 @@
         </is>
       </c>
       <c r="T2" t="n">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="U2" t="n">
         <v>13</v>
@@ -8589,17 +9203,17 @@
         <v>34</v>
       </c>
       <c r="W2" t="n">
-        <v>162</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C3" t="n">
         <v>13</v>
@@ -8608,7 +9222,7 @@
         <v>34</v>
       </c>
       <c r="E3" t="n">
-        <v>7</v>
+        <v>162</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -8631,7 +9245,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -8644,6 +9258,25 @@
         <v>34</v>
       </c>
       <c r="E4" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>161</v>
+      </c>
+      <c r="C5" t="n">
+        <v>13</v>
+      </c>
+      <c r="D5" t="n">
+        <v>34</v>
+      </c>
+      <c r="E5" t="n">
         <v>7</v>
       </c>
     </row>
